--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T10:31:14+00:00</t>
+    <t>2026-02-04T11:03:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T11:03:32+00:00</t>
+    <t>2026-02-06T08:16:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T08:16:26+00:00</t>
+    <t>2026-02-06T09:56:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T09:56:58+00:00</t>
+    <t>2026-02-06T10:49:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-task-transport|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-task-transport</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -925,7 +925,7 @@
     <t>The title (eg "My Tasks", "Outstanding Tasks for Patient X") should go into the code.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-mode-de-transport-cisis|20250624152101</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-mode-de-transport-cisis</t>
   </si>
   <si>
     <t>typeTransport</t>
@@ -977,7 +977,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner)
 </t>
   </si>
   <si>
@@ -1005,7 +1005,7 @@
     <t>Task.encounter</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-encounter-evenement|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-encounter-evenement)
 </t>
   </si>
   <si>
@@ -1220,7 +1220,7 @@
 Executer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-organization|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-organization)
 </t>
   </si>
   <si>
@@ -1525,7 +1525,7 @@
     <t>Inputs are named to enable task automation to bind data and pass it from one task to the next.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/input-tddui-task-transport-valueset|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-task-input-transport</t>
   </si>
   <si>
     <t>Task.input.value[x]</t>
@@ -1564,7 +1564,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-transport"/&gt;
     &lt;code value="typeMotorisation"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1573,7 +1573,7 @@
     <t>Task.input:typeMotorisation.value[x]</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-type-motorisation-cisis|20250624152100</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-type-motorisation-cisis</t>
   </si>
   <si>
     <t>Task.input:adresseDepart</t>
@@ -1599,7 +1599,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-transport"/&gt;
     &lt;code value="adresseDepart"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1635,7 +1635,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-transport"/&gt;
     &lt;code value="adresseDestination"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1667,7 +1667,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-transport"/&gt;
     &lt;code value="budgetPrevisionnel"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1703,7 +1703,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-transport"/&gt;
     &lt;code value="budgetReel"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1735,7 +1735,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-transport"/&gt;
     &lt;code value="distance"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1771,7 +1771,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/input-tddui-task-transport-codesystem"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-task-input-transport"/&gt;
     &lt;code value="dureeTheorique"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -2159,7 +2159,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="143.0390625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="78.97265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="62.203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T10:49:33+00:00</t>
+    <t>2026-02-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T10:00:25+00:00</t>
+    <t>2026-02-11T15:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T15:08:15+00:00</t>
+    <t>2026-02-12T14:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T14:50:08+00:00</t>
+    <t>2026-02-16T09:17:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:17:35+00:00</t>
+    <t>2026-02-16T09:32:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:32:48+00:00</t>
+    <t>2026-02-16T14:58:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T14:58:48+00:00</t>
+    <t>2026-02-23T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T15:44:46+00:00</t>
+    <t>2026-02-24T10:21:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T10:21:42+00:00</t>
+    <t>2026-02-24T16:53:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T16:53:25+00:00</t>
+    <t>2026-02-25T09:45:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T09:45:56+00:00</t>
+    <t>2026-02-26T08:21:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-task-transport-professionnel.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T08:21:36+00:00</t>
+    <t>2026-02-26T10:20:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
